--- a/src/Tests.Skia/ExcelValidationTests.ValidationsAndRequiredAndLocked.verified.xlsx
+++ b/src/Tests.Skia/ExcelValidationTests.ValidationsAndRequiredAndLocked.verified.xlsx
@@ -81,5 +81,6 @@
       <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
--- a/src/Tests.Skia/ExcelValidationTests.ValidationsAndRequiredAndLocked.verified.xlsx
+++ b/src/Tests.Skia/ExcelValidationTests.ValidationsAndRequiredAndLocked.verified.xlsx
@@ -81,6 +81,5 @@
       <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>